--- a/data/incorrect-instances_gpt-4o-mini-1.xlsx
+++ b/data/incorrect-instances_gpt-4o-mini-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\scripts\hil\hil-test-case-gen\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD7F04B-85F0-4CCF-AEC6-BF78AA58ECCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3DCB28-B2D4-45BA-BF31-E1FA7BA52FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
